--- a/projects/components/cache-ip/amber-mesi-l1/docs/amber_signal_contracts.xlsx
+++ b/projects/components/cache-ip/amber-mesi-l1/docs/amber_signal_contracts.xlsx
@@ -1187,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1343,17 +1343,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>AR/AW</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>m_axi_rack</t>
+          <t>m_axi_ardomain[1:0] / m_axi_awdomain[1:0]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>axi4ace_master_rd</t>
+          <t>amber_ace_top</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>ACE read acknowledge, auto-pulsed one cycle after RLAST handshake.</t>
+          <t>Tied 0b10 Outer Shareable: every amber transaction is coherent and the rig has one shareability domain (IHI 0022H Tables D3-7 / D3-8).</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>exactly one rack per read transaction</t>
+          <t>constant 0b10 on every AR and AW</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -1385,17 +1385,17 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>AW</t>
+          <t>AR/AW</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>fub_axi_awsnoop[2:0]</t>
+          <t>m_axi_arbar[1:0] / m_axi_awbar[1:0]</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>amber_ace_issue</t>
+          <t>amber_ace_top</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>CleanUnique, MakeUnique, WriteBack, or Evict per cache event.</t>
+          <t>Tied 0b00, normal access respecting barriers; amber issues no barrier transactions (onyx D8).</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>awsnoop is one of the four onyx-D2 write encodings</t>
+          <t>constant 0b00 on every AR and AW</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1427,37 +1427,37 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>AW/W</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>fub_axi_awvalid / wvalid / wlast</t>
+          <t>m_axi_rresp[3:0]</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>out</t>
+          <t>in</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>amber_drain / axi4ace_master_wr</t>
+          <t>manager (onyx)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>WriteBack carries W data; CleanUnique/MakeUnique/Evict are AW-only.</t>
+          <t>[1:0] AXI response to the fill engine; [3:2] IsShared/PassDirty carried and monitored but not consumed (install state follows the request class).</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>wlast exactly once per WriteBack; no W data for CU/MU/Evict</t>
+          <t>PassDirty LOW on every ReadShared response (amber cannot absorb dirty data into S)</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1469,40 +1469,166 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>m_axi_rack</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>axi4ace_master_rd</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>ACE read acknowledge, auto-pulsed one cycle after RLAST handshake.</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>exactly one rack per read transaction</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/cache-ip/amber-mesi-l1/docs/amber_has/ch04_interfaces/03_fabric_ace.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>AW</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>fub_axi_awsnoop[2:0]</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>amber_ace_issue</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>CleanUnique, MakeUnique, WriteBack, or Evict per cache event.</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>awsnoop is one of the four onyx-D2 write encodings</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/cache-ip/amber-mesi-l1/docs/amber_has/ch04_interfaces/03_fabric_ace.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AW/W</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>fub_axi_awvalid / wvalid / wlast</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>out</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>amber_drain / axi4ace_master_wr</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>WriteBack carries W data; CleanUnique/MakeUnique/Evict are AW-only.</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>wlast exactly once per WriteBack; no W data for CU/MU/Evict</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/cache-ip/amber-mesi-l1/docs/amber_has/ch04_interfaces/03_fabric_ace.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>m_axi_wack</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>axi4ace_master_wr</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>ACE write acknowledge, auto-pulsed one cycle after B handshake.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>exactly one wack per write transaction</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>projects/components/cache-ip/amber-mesi-l1/docs/amber_has/ch04_interfaces/03_fabric_ace.md</t>
         </is>
